--- a/artfynd/A 59076-2025 artfynd.xlsx
+++ b/artfynd/A 59076-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73778156</v>
+        <v>73778142</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731941.8505310573</v>
+        <v>731995</v>
       </c>
       <c r="R2" t="n">
-        <v>7183496.928547756</v>
+        <v>7183610</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-10-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73778142</v>
+        <v>73778156</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731995.0521891246</v>
+        <v>731942</v>
       </c>
       <c r="R3" t="n">
-        <v>7183610.101690787</v>
+        <v>7183497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2018-10-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>73778192</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731943.1985807681</v>
+        <v>731943</v>
       </c>
       <c r="R4" t="n">
-        <v>7183496.173433786</v>
+        <v>7183496</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2018-10-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59076-2025 artfynd.xlsx
+++ b/artfynd/A 59076-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778156</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>